--- a/InputData/land/AOCoLUPpUA/Annual Ongoing Cost of Land Use Pol per Unit Area.xlsx
+++ b/InputData/land/AOCoLUPpUA/Annual Ongoing Cost of Land Use Pol per Unit Area.xlsx
@@ -1,45 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20416"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\land\AOCoLUPpUA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\minhe\Dropbox\01. NEXT Group\00. NEXT Group\20. 프로젝트 관리\2025 에너지 수요전망 모형 구축\EPS 모형\eps-southkorea-3.3.1\InputData\land\AOCoLUPpUA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF94B7C1-28EB-4AAB-A6C5-9A13131631C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0342AB9-CBDD-4140-B4B8-B8251C13B46A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11205" yWindow="840" windowWidth="20520" windowHeight="15465" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="AOCoLUPpUA" sheetId="3" r:id="rId2"/>
+    <sheet name="Cal" sheetId="8" r:id="rId2"/>
+    <sheet name="AOCoLUPpUA" sheetId="3" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
     <definedName name="C_to_CO2">'[1]Conversion Factors'!$A$4</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
   <si>
     <t>AOCoLUPpUA Annual Ongoing Cost of Land Use Policies per Unit Area</t>
   </si>
@@ -47,54 +36,206 @@
     <t>Source:</t>
   </si>
   <si>
+    <t>forest set asides</t>
+  </si>
+  <si>
+    <t>afforestation and reforestation</t>
+  </si>
+  <si>
+    <t>improved forest management</t>
+  </si>
+  <si>
+    <t>avoid deforestation</t>
+  </si>
+  <si>
+    <t>peatland restoration</t>
+  </si>
+  <si>
+    <t>forest restoration</t>
+  </si>
+  <si>
+    <t>annual maintenance cost ($ / acre)</t>
+  </si>
+  <si>
     <t>Notes</t>
-  </si>
-  <si>
-    <t>forest set asides</t>
-  </si>
-  <si>
-    <t>afforestation and reforestation</t>
-  </si>
-  <si>
-    <t>improved forest management</t>
-  </si>
-  <si>
-    <t>avoid deforestation</t>
-  </si>
-  <si>
-    <t>peatland restoration</t>
-  </si>
-  <si>
-    <t>forest restoration</t>
-  </si>
-  <si>
-    <t>annual maintenance cost ($ / acre)</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Based on consultation with the organization American Forests, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">annual ongoing for land affected by these policy levers is a </t>
-  </si>
-  <si>
-    <t>small part of lifetime costs. For this reason, we do not attempt</t>
-  </si>
-  <si>
-    <t>to track these in the US model.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unit</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ha</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>acre</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>산림병해충별 사업비 및 사업면적</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>솔잎혹파리</t>
+  </si>
+  <si>
+    <t>사업비</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업면적</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>won</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ha</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>솔껍질깍지벌레</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>참나무시들음병</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타병해충</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>won/ha</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업비/사업면적 가중평균치</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ha당 비료비용</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>years</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>시비란, 수목이 잘 성장할 수 있도록 천연 또는 인공의 양분을 공급하는 수목관리의 한 방법</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>total</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>won/ha</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>won/acre</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>USD</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>$/acre</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Page 66, 77, 83, 93</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.forest.go.kr/kfsweb/cmm/fms/FileDown.do;jsessionid=C75neeKhp9P7wk1NBQknRfKjHd53CUaCoAns1Gd3x9pJ6s2sJe4fZX2YEH3dtfEe.frswas02_servlet_engine5?atchFileId=FILE_000000020025108&amp;fileSn=0&amp;dwldHistYn=N&amp;bbsId=BBSMSTR_1069</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Page 4</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Avoid deforestion, peatland restoration, and forest restoration policies</t>
+  </si>
+  <si>
+    <t>are not used in the U.S. version of the model.</t>
+  </si>
+  <si>
+    <t>This variable is for the costs to maintain lands previously affected by one of the</t>
+  </si>
+  <si>
+    <t>land use policies (such as "Afforestation/Reforestation") and thereby</t>
+  </si>
+  <si>
+    <t>avoid emission of sequestered CO2.</t>
+  </si>
+  <si>
+    <t>This variable is NOT for use with the Improved Forest Management policy,</t>
+  </si>
+  <si>
+    <t>as that policy must be repeated every year in order to obtain carbon benefits</t>
+  </si>
+  <si>
+    <t>in that year.  Its cost is handled in the "Implementation Cost of Land Use</t>
+  </si>
+  <si>
+    <t>Policies per Unit Area" variable.</t>
+  </si>
+  <si>
+    <t>Both new forests (from afforestation/reforestation) and forests set aside from</t>
+  </si>
+  <si>
+    <t>timber harvesting need to be managed.</t>
+  </si>
+  <si>
+    <t>Cost of pest control per ha</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Department of Forest</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Korea Forest Research Institute</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>News Article</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Forest disease and pestcontrol plan</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Estimation of fertilizer cost per hectare</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.forest.go.kr/newkfsweb/cmm/fms/BoardFileDown.do?atchFileId=FILE_000000000355787&amp;fileSn=1&amp;dwldHistYn=N&amp;bbsId=BBSMSTR_1036&amp;fn=%EC%82%B0%EB%B6%88%ED%94%BC%ED%95%B4%EC%A7%80%20%EB%A7%9E%EC%B6%A4%ED%98%95%20%EB%B9%84%EB%A3%8C%EB%A1%9C%20%EC%A1%B0%EA%B8%B0%EB%B3%B4%EA%B5%AC%20%EC%95%9E%EB%8B%B9%EA%B2%A8(%EA%B5%AD%EB%A6%BD%EC%82%B0%EB%A6%BC%EA%B3%BC%ED%95%99%EC%9B%90!).hwp</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="178" formatCode="0_ "/>
+  </numFmts>
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -102,14 +243,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -117,7 +258,7 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -125,17 +266,98 @@
       <b/>
       <sz val="12"/>
       <color theme="4"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -183,7 +405,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="7">
+  <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFont="0" applyProtection="0">
       <alignment wrapText="1"/>
@@ -201,22 +423,72 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="7"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="3" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="7" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="9">
     <cellStyle name="Body: normal cell" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Font: Calibri, 9pt regular" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Footnotes: top row" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Header: bottom row" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Parent row" xfId="5" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Table title" xfId="6" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="쉼표 [0]" xfId="8" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="7" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -229,6 +501,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>620005</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>162299</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8223F760-2A4F-4576-9B1B-9CB4872978BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3562350"/>
+          <a:ext cx="6306430" cy="2676899"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -289,7 +610,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -609,129 +930,610 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B12" s="21">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B13" s="22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B14" s="23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B15" s="22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="B18" s="7">
+        <v>1</v>
+      </c>
+      <c r="C18" s="7"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="1:2" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:2" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="1:2" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="1:2" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="1:2" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="1:1" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:1" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:1" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
+      <c r="B19" s="8">
+        <v>2.4710540000000001</v>
+      </c>
+      <c r="C19" s="7"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B20" s="14">
+        <v>1179.9000000000001</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB946260-02EE-442B-AB48-95C4123D611A}">
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="7"/>
+    <col min="2" max="2" width="13.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="7">
+        <v>4761</v>
+      </c>
+      <c r="C3" s="7">
+        <v>505</v>
+      </c>
+      <c r="D3" s="7">
+        <v>5451</v>
+      </c>
+      <c r="E3" s="7">
+        <v>13642</v>
+      </c>
+      <c r="F3" s="9">
+        <v>1000000</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="7">
+        <v>5333</v>
+      </c>
+      <c r="C4" s="7">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="D4" s="7">
+        <f>674+3998</f>
+        <v>4672</v>
+      </c>
+      <c r="E4" s="7">
+        <v>52260</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F5" s="10"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="7">
+        <f>SUMPRODUCT(B3:E3,B4:E4)/SUM(B4:E4)</f>
+        <v>12254.641499716827</v>
+      </c>
+      <c r="F6" s="9">
+        <v>1000000</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E7" s="12">
+        <f>E6/SUM($B$4:$E$4)*F3</f>
+        <v>196611.8795188255</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="7">
+        <v>3</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="9">
+        <v>567000</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="7">
+        <v>1</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="13">
+        <f>C24/$A$24</f>
+        <v>189000</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B29" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="12">
+        <f>E7+C25</f>
+        <v>385611.8795188255</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C30" s="11">
+        <f>C29/About!B19</f>
+        <v>156051.57941462449</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C31" s="11">
+        <f>C30/About!B20</f>
+        <v>132.25830953015043</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B3" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B4" s="16">
+        <f>Cal!C31</f>
+        <v>132.25830953015043</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81B8D0BD-5CE8-4D2C-8F66-23CB3DD60907}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20034FA4-D942-4AE3-A44C-3C8479018C3F}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0746B9E9-AE4D-4D13-851D-4EFF62BDDADA}"/>
 </file>